--- a/design/tables/LevelLoadout.xlsx
+++ b/design/tables/LevelLoadout.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelLoadout" sheetId="1" r:id="R7c4efe4780ab45b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelLoadout" sheetId="1" r:id="Rff0196a7bebb4a32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -785,16 +785,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C26" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D26" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="2" t="str">
-        <x:v>frost|bloom|scope|mint</x:v>
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
       </x:c>
       <x:c r="F26" s="2" t="str">
-        <x:v>frost|bloom|scope|mint</x:v>
+        <x:v>sprout|frost|bloom|scope</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/LevelLoadout.xlsx
+++ b/design/tables/LevelLoadout.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelLoadout" sheetId="1" r:id="Rff0196a7bebb4a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelLoadout" sheetId="1" r:id="Rdb23f382f0544044"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -797,6 +797,106 @@
         <x:v>sprout|frost|bloom|scope</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>sprout|frost|scope|fan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>sprout|bloom|ember|scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>sprout|frost|spark|fan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>sprout|frost|bloom|mint</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/LevelLoadout.xlsx
+++ b/design/tables/LevelLoadout.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelLoadout" sheetId="1" r:id="Rdb23f382f0544044"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelLoadout" sheetId="1" r:id="Rd0ae2739a6b54c64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -275,6 +275,7 @@
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="65" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="41.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="44" customHeight="1">
@@ -296,6 +297,9 @@
       <x:c r="F1" s="3" t="str">
         <x:v>默认阵容</x:v>
       </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>阵容持久化键（唯一，兼容旧专题）</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -316,6 +320,9 @@
       <x:c r="F2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="G2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -336,6 +343,9 @@
       <x:c r="F3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="3" t="str">
@@ -356,6 +366,9 @@
       <x:c r="F4" s="3" t="str">
         <x:v>默认阵容</x:v>
       </x:c>
+      <x:c r="G4" s="3" t="str">
+        <x:v>阵容持久化键（唯一，兼容旧专题）</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -376,6 +389,9 @@
       <x:c r="F5" s="5" t="str">
         <x:v>defaultStaff</x:v>
       </x:c>
+      <x:c r="G5" s="5" t="str">
+        <x:v>storageKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="2" t="n">
@@ -395,6 +411,9 @@
       </x:c>
       <x:c r="F6" s="2" t="str">
         <x:v>sprout</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="str">
+        <x:v>night_store_loadout_v1_1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -416,6 +435,9 @@
       <x:c r="F7" s="2" t="str">
         <x:v>sprout|frost</x:v>
       </x:c>
+      <x:c r="G7" s="2" t="str">
+        <x:v>night_store_loadout_v1_2</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="2" t="n">
@@ -436,6 +458,9 @@
       <x:c r="F8" s="2" t="str">
         <x:v>sprout|frost|bloom</x:v>
       </x:c>
+      <x:c r="G8" s="2" t="str">
+        <x:v>night_store_loadout_v1_3</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="2" t="n">
@@ -455,6 +480,9 @@
       </x:c>
       <x:c r="F9" s="2" t="str">
         <x:v>sprout|frost|bloom</x:v>
+      </x:c>
+      <x:c r="G9" s="2" t="str">
+        <x:v>night_store_loadout_v1_4</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
@@ -476,6 +504,9 @@
       <x:c r="F10" s="2" t="str">
         <x:v>sprout|frost|bloom</x:v>
       </x:c>
+      <x:c r="G10" s="2" t="str">
+        <x:v>night_store_loadout_v1_5</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="2" t="n">
@@ -496,6 +527,9 @@
       <x:c r="F11" s="2" t="str">
         <x:v>sprout|frost|bloom|scope</x:v>
       </x:c>
+      <x:c r="G11" s="2" t="str">
+        <x:v>night_store_loadout_v1_6</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="2" t="n">
@@ -516,6 +550,9 @@
       <x:c r="F12" s="2" t="str">
         <x:v>sprout|frost|bloom|scope</x:v>
       </x:c>
+      <x:c r="G12" s="2" t="str">
+        <x:v>night_store_loadout_v1_7</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="2" t="n">
@@ -536,6 +573,9 @@
       <x:c r="F13" s="2" t="str">
         <x:v>scope|frost|bloom|spark</x:v>
       </x:c>
+      <x:c r="G13" s="2" t="str">
+        <x:v>night_store_loadout_v1_8</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="2" t="n">
@@ -556,6 +596,9 @@
       <x:c r="F14" s="2" t="str">
         <x:v>scope|frost|bloom|spark</x:v>
       </x:c>
+      <x:c r="G14" s="2" t="str">
+        <x:v>night_store_loadout_v1_9</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
       <x:c r="A15" s="2" t="n">
@@ -576,6 +619,9 @@
       <x:c r="F15" s="2" t="str">
         <x:v>scope|frost|bloom|spark</x:v>
       </x:c>
+      <x:c r="G15" s="2" t="str">
+        <x:v>night_store_loadout_v1_10</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="44" customHeight="1">
       <x:c r="A16" s="2" t="n">
@@ -596,6 +642,9 @@
       <x:c r="F16" s="2" t="str">
         <x:v>sprout|frost|bloom|ember</x:v>
       </x:c>
+      <x:c r="G16" s="2" t="str">
+        <x:v>night_store_loadout_v1_11</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="2" t="n">
@@ -616,6 +665,9 @@
       <x:c r="F17" s="2" t="str">
         <x:v>scope|frost|bloom|ember</x:v>
       </x:c>
+      <x:c r="G17" s="2" t="str">
+        <x:v>night_store_loadout_v1_12</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="44" customHeight="1">
       <x:c r="A18" s="2" t="n">
@@ -636,6 +688,9 @@
       <x:c r="F18" s="2" t="str">
         <x:v>sprout|bloom|mint|ember</x:v>
       </x:c>
+      <x:c r="G18" s="2" t="str">
+        <x:v>night_store_loadout_v1_13</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="44" customHeight="1">
       <x:c r="A19" s="2" t="n">
@@ -656,6 +711,9 @@
       <x:c r="F19" s="2" t="str">
         <x:v>scope|spark|mint|frost</x:v>
       </x:c>
+      <x:c r="G19" s="2" t="str">
+        <x:v>night_store_loadout_v1_14</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
       <x:c r="A20" s="2" t="n">
@@ -676,6 +734,9 @@
       <x:c r="F20" s="2" t="str">
         <x:v>scope|bloom|ember|mint</x:v>
       </x:c>
+      <x:c r="G20" s="2" t="str">
+        <x:v>night_store_loadout_v1_15</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="44" customHeight="1">
       <x:c r="A21" s="2" t="n">
@@ -696,6 +757,9 @@
       <x:c r="F21" s="2" t="str">
         <x:v>sprout|frost|bloom|fan</x:v>
       </x:c>
+      <x:c r="G21" s="2" t="str">
+        <x:v>night_store_loadout_v1_16</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="2" t="n">
@@ -716,6 +780,9 @@
       <x:c r="F22" s="2" t="str">
         <x:v>scope|spark|frost|fan</x:v>
       </x:c>
+      <x:c r="G22" s="2" t="str">
+        <x:v>night_store_loadout_v1_17</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="44" customHeight="1">
       <x:c r="A23" s="2" t="n">
@@ -736,6 +803,9 @@
       <x:c r="F23" s="2" t="str">
         <x:v>scope|bloom|mint|fan</x:v>
       </x:c>
+      <x:c r="G23" s="2" t="str">
+        <x:v>night_store_loadout_v1_18</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="2" t="n">
@@ -756,6 +826,9 @@
       <x:c r="F24" s="2" t="str">
         <x:v>scope|frost|ember|fan</x:v>
       </x:c>
+      <x:c r="G24" s="2" t="str">
+        <x:v>night_store_loadout_v1_19</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="44" customHeight="1">
       <x:c r="A25" s="2" t="n">
@@ -776,13 +849,16 @@
       <x:c r="F25" s="2" t="str">
         <x:v>scope|frost|bloom|mint</x:v>
       </x:c>
+      <x:c r="G25" s="2" t="str">
+        <x:v>night_store_loadout_v1_20</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="44" customHeight="1">
       <x:c r="A26" s="2" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="2" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="2" t="n">
         <x:v>1</x:v>
@@ -796,13 +872,16 @@
       <x:c r="F26" s="2" t="str">
         <x:v>sprout|frost|bloom|scope</x:v>
       </x:c>
+      <x:c r="G26" s="2" t="str">
+        <x:v>night_store_loadout_v1_21</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B27" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" t="n">
         <x:v>1</x:v>
@@ -816,13 +895,16 @@
       <x:c r="F27" t="str">
         <x:v>sprout|frost|scope|fan</x:v>
       </x:c>
+      <x:c r="G27" t="str">
+        <x:v>night_store_loadout_v1_22</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="n">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B28" t="n">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C28" t="n">
         <x:v>1</x:v>
@@ -836,13 +918,16 @@
       <x:c r="F28" t="str">
         <x:v>sprout|bloom|ember|scope</x:v>
       </x:c>
+      <x:c r="G28" t="str">
+        <x:v>night_store_loadout_v1_23</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="n">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B29" t="n">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C29" t="n">
         <x:v>1</x:v>
@@ -856,13 +941,16 @@
       <x:c r="F29" t="str">
         <x:v>sprout|frost|spark|fan</x:v>
       </x:c>
+      <x:c r="G29" t="str">
+        <x:v>night_store_loadout_v1_24</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B30" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C30" t="n">
         <x:v>1</x:v>
@@ -876,25 +964,353 @@
       <x:c r="F30" t="str">
         <x:v>sprout|frost|bloom|mint</x:v>
       </x:c>
+      <x:c r="G30" t="str">
+        <x:v>night_store_loadout_v1_25</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>night_store_loadout_v1_26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C32" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E32" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F32" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G32" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B33" s="2" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C33" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D33" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E33" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F33" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G33" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B34" s="2" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C34" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E34" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F34" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G34" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B35" s="2" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C35" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E35" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F35" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G35" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B36" s="2" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E36" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F36" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G36" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B31" t="n">
+      <x:c r="B37" s="2" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>scope|frost|bloom|mint</x:v>
+      <x:c r="C37" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F37" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G37" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E38" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F38" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G38" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E39" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F39" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G39" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C40" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E40" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F40" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G40" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B41" s="2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C41" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E41" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F41" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G41" s="2" t="str">
+        <x:v>night_store_adventure_loadout_v1_30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="2" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="2" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C42" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E42" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F42" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G42" s="2" t="str">
+        <x:v>night_store_challenge_loadout_v1_freezer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="2" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" s="2" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C43" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D43" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E43" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F43" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G43" s="2" t="str">
+        <x:v>night_store_challenge_loadout_v1_gifts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="2" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B44" s="2" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C44" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D44" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E44" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F44" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G44" s="2" t="str">
+        <x:v>night_store_challenge_loadout_v1_storm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="2" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B45" s="2" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C45" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D45" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E45" s="2" t="str">
+        <x:v>sprout|frost|bloom|scope|spark|ember|mint|fan</x:v>
+      </x:c>
+      <x:c r="F45" s="2" t="str">
+        <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="G45" s="2" t="str">
+        <x:v>night_store_challenge_loadout_v1_dawn</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
